--- a/신고신저가_20260804.xlsx
+++ b/신고신저가_20260804.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -76,18 +77,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 미 실적시즌 산업재·금융 어닝 서프라이즈로 3대지수 동반 상승(위험선호 재개), 반면 중화권은 반도체·AI하드웨어 급락 디커플링. 일본은 파나크 실적 쇼크로 전섹터 약세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(한국시간 8/4 새벽 마감, 현지 8/3장): 나스닥+2.1%·S&amp;P+1.5%·다우+1.3%. 강세=금융(순강도+22, 신고22·12MF PER15.5)·산업재(XLI+1.8%)·커뮤니케이션(XLC+2.9%), 약세=에너지(XLE-1.3%). 이튼·CNH·인거솔랜드 실적호조 신고 러시; 매리어트(중동 RevPAR-43%)·아스트라제네카(BMS 합병설)·FICO(강등) 급락.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/3 마감): 신고0/신저7 전섹터 약세. 파나크 -14%(Q1 실적·가이던스 실망, 약 40년만 최대낙폭)가 주도, 아이신 -3.6%. 부동산·자동차 업종ETF -4%대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/3): 항셍+0.5%·항셍테크+1.0% 소폭강세. 금융 강세(지투글로벌·프라다 신고), 반도체는 약세(중신궈지 신저).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/3): 상해-0.6%·CSI300-1.0% 약세. 반도체ETF -7.2%(주간-18%·1M-31%) 붕괴, 통푸마이크로-9.5%·리쉰정밀-6.6% 신저 몰림. 은행(흥업)·해운(코스코)만 방어 신고.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①미 산업재·금융 어닝 모멘텀 지속 여부 ②중화권 반도체 급락 바닥 확인 ③파나크발 일본 FA·자동차 투심 전이.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +756,19 @@
       <c r="C2" t="n">
         <v>7600.5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>2.53</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="4" t="n">
         <v>5.12</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="4" t="n">
         <v>11.03</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +794,19 @@
       <c r="C3" t="n">
         <v>25913.9</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>2.13</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>3.94</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="4" t="n">
         <v>0.31</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>3.18</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="4" t="n">
         <v>11.5</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +832,19 @@
       <c r="C4" t="n">
         <v>6595.45</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="4" t="n">
         <v>17.91</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>-1.42</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>-20.57</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="4" t="n">
         <v>56.51</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +870,19 @@
       <c r="C5" t="n">
         <v>64362.02</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>4.03</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>-0.39</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="5" t="n">
         <v>-8.67</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="4" t="n">
         <v>7.42</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="4" t="n">
         <v>27.86</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +908,19 @@
       <c r="C6" t="n">
         <v>3809.66</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>-0.59</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>-1.26</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>-5.79</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>-7.36</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="5" t="n">
         <v>-4.01</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +946,19 @@
       <c r="C7" t="n">
         <v>4543.18</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.98</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>-3.39</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="5" t="n">
         <v>-6.17</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="5" t="n">
         <v>-5.49</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>-1.87</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +984,19 @@
       <c r="C8" t="n">
         <v>26009.4</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>3.18</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="4" t="n">
         <v>11.39</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>1.48</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1022,19 @@
       <c r="C9" t="n">
         <v>4875.61</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>3.69</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.09</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="5" t="n">
         <v>-11.61</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1153,7 @@
       <c r="F2" t="n">
         <v>22</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1194,7 @@
       <c r="F3" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1235,7 @@
       <c r="F4" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1276,7 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1317,7 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1358,7 @@
       <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1399,7 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1440,7 @@
       <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1481,7 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1522,7 @@
       <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1563,7 @@
       <c r="F12" t="n">
         <v>-1</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1557,7 +1604,7 @@
       <c r="F13" t="n">
         <v>-2</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1598,7 +1645,7 @@
       <c r="F14" t="n">
         <v>-2</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1971,7 @@
       <c r="F22" t="n">
         <v>-1</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1965,7 +2012,7 @@
       <c r="F23" t="n">
         <v>-1</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2006,7 +2053,7 @@
       <c r="F24" t="n">
         <v>-2</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2045,7 +2092,7 @@
       <c r="F25" t="n">
         <v>-3</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2638,7 +2685,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2679,7 +2726,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2720,7 +2767,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2761,7 +2808,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2802,7 +2849,7 @@
       <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2843,7 +2890,7 @@
       <c r="F45" t="n">
         <v>-2</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3362,7 +3409,7 @@
       <c r="F58" t="n">
         <v>2</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3403,7 +3450,7 @@
       <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3442,7 +3489,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3483,7 +3530,7 @@
       <c r="F61" t="n">
         <v>-1</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3522,7 +3569,7 @@
       <c r="F62" t="n">
         <v>-2</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3563,7 +3610,7 @@
       <c r="F63" t="n">
         <v>-3</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4066,30 +4113,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4110,90 +4158,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4215,58 +4268,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>테크 +1.5%, 나스닥 강세 견인. 순강도+10 강세 지속(12MF PER 22.9)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4286,58 +4344,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>헬스케어 -0.2% 부진, 아스트라제네카 BMS 합병설 급락 부담</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4357,58 +4420,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>금융 +0.8%, 신고22·순강도+22 미 최강 섹터. 실적시즌 수혜(PER 15.5)</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4428,58 +4496,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>경기소비재 +1.8% 강세, 위험선호 재개. 단 매리어트는 가이던스 하회로 급락</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>6.6</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4499,58 +4572,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>커뮤니케이션 +2.9% 당일 최강, 대형테크 랠리 주도</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4570,58 +4648,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>산업재 +1.8%, 이튼·CNH·인거솔랜드 실적호조로 신고 러시</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4641,58 +4724,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>필수소비재 -0.2%, 방어주 소외(위험선호 국면)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4712,58 +4800,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>에너지 -1.3% 당일 최약, 유가 약세. 단 1M +10.5%로 중기 강세는 유지</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4783,58 +4876,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>유틸리티 보합, 주간 -2.9%로 약세 지속</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4854,58 +4952,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>소재 +1.2% 반등, 순강도+1 강세 전환</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4925,58 +5028,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>리츠 +0.2% 강보합, 금리 부담 속 상승폭 제한</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4996,58 +5104,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>16.9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5067,58 +5176,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>7.7</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5138,58 +5248,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5209,58 +5320,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5280,58 +5392,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>15</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5351,58 +5464,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5422,58 +5536,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-16.2</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5493,58 +5608,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5564,58 +5680,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-8.9</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>28.9</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5635,58 +5752,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>6.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5706,58 +5824,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>14</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5777,58 +5896,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5848,58 +5968,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5919,58 +6040,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5990,58 +6112,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-7</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6061,58 +6184,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>28.5</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6132,58 +6256,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-12.1</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6203,58 +6328,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6274,58 +6400,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-12.8</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-17.8</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.6</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6345,56 +6472,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-11.3</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6412,58 +6540,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>반도체 -7.2% 급락(주간-18%·1M-31%), 통푸마이크로·리쉰정밀 신저 주도. 섹터 붕괴</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-18.1</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-30.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.2</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6483,58 +6616,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>테크 -4.2%, 반도체발 성장주 동반 급락</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6554,58 +6692,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>5G통신 -1.6%, 주간-14% 약세 지속</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-14.5</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-27.1</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-8.5</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6625,56 +6768,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>신에너지차 -0.3% 강보합, 당일 낙폭 제한</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-24.3</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6692,58 +6840,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>방산 +0.7% 소폭강세, 낙폭과대 반등(YTD-19.8% 부진)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-15.4</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-21.3</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-19.8</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>12</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6763,56 +6916,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>태양광 +2.0% 당일 최강, 낙폭과대 기술적 반등</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>-13.1</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-21.7</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-13.5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>9</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6830,58 +6988,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>백주 -1.1% 조정, 소비 약세. 단 1M +13%로 회복세</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>6.7</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-7.4</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-16.4</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6901,58 +7064,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>은행 -0.6% 소폭조정이나 흥업은행 신고, 방어주 선호 지속(1M+11%)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>4</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6972,58 +7140,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유색금속 -0.8%, 3M-16% 약세 국면</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-16.1</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-7.7</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7043,58 +7216,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>부동산 +0.5% 강보합, 정책기대 잔존</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-17</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-20.3</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7114,58 +7292,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>증권 -0.2% 보합, 거래 모멘텀 부진</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7185,58 +7368,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>의약 -0.8% 약보합</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7256,58 +7444,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>소비 -1.0%, 내수 부진 반영(YTD-13%)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-7.6</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>8</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7319,7 +7512,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-7.2"/>
@@ -7331,7 +7524,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-18.1"/>
@@ -7343,7 +7536,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-30.8"/>
@@ -7355,7 +7548,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.3"/>
@@ -7367,7 +7560,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-20.3"/>
@@ -7379,7 +7572,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7391,7 +7584,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7403,7 +7596,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7415,7 +7608,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7427,7 +7620,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7439,7 +7632,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7553,7 +7746,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7602,19 +7795,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) 마이크로소프트(클라우드·AI): FY4Q 애저 매출 43% 성장·연매출 첫 1000억달러 돌파 서프라이즈</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7662,15 +7855,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7716,15 +7909,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7772,15 +7965,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7828,15 +8021,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7880,15 +8073,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7932,15 +8125,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>텍사스인스트루먼트(아날로그반도체): 실적 강세에도 Q3 가이던스 실망·반도체 차익실현 매물에 시장 역행 하락</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7984,15 +8181,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>아스트라제네카(글로벌 제약): BMS와 대형 합병 예비협상 보도에 희석·전략 합리성 의문으로 투자자 이탈 급락</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8034,15 +8235,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8084,15 +8285,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8140,15 +8341,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>이튼(전력관리·전기장비): Q2 EPS·매출 상회, 전력인프라 수주 급증·FY26 가이던스 상향, 에버코어 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8192,10 +8397,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8248,15 +8453,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8300,10 +8505,10 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8354,19 +8559,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 스노우플레이크(클라우드 데이터플랫폼): 웰스파고 목표가 $320→$500 상향·AI에이전트 지출 가속 논거</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8410,15 +8615,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8460,15 +8665,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8512,15 +8717,15 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8562,15 +8767,19 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" s="7" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>매리어트(글로벌 호텔체인): Q2 매출 컨센 소폭 미달, 중동 RevPAR -43% 급락·Q3 EPS 가이던스 하회로 급락</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8614,15 +8823,15 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8666,15 +8875,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8718,15 +8927,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8774,10 +8983,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8826,19 +9035,19 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>(전일) 리제네론(항체 의약품·듀피젠트): 2분기 EPS $14.29로 컨센서스 $10.53 대폭 초과, 급등</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8886,15 +9095,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8942,10 +9151,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="7" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8994,10 +9203,10 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="7" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9050,15 +9259,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="7" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9106,10 +9315,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9162,15 +9371,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9214,15 +9423,15 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="7" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9270,15 +9479,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="7" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9322,15 +9531,19 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="7" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr">
+        <is>
+          <t>인거솔랜드(산업용 압축기·펌프): Q2 실적·가이던스 상향, Baird 목표가 상향에 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9378,15 +9591,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="7" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9430,10 +9643,10 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="7" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9486,19 +9699,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="7" t="inlineStr">
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>(전일) 덱스콤(연속혈당측정기): 2Q EPS·매출 상회, 연간 가이던스 소폭 상향으로 급등</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9542,15 +9755,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="7" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9594,10 +9807,10 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="7" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9650,14 +9863,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="7" t="inlineStr">
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>(전일) 일루미나(유전자 시퀀싱 장비): 2분기 실적 상회·NovaSeq X 수요 호조로 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9706,19 +9919,19 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr">
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>(전일) LPL파이낸셜(독립 투자자문 플랫폼): 2Q EPS·매출 컨센 상회, 어드바이저 유치 호조</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9762,15 +9975,15 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9818,15 +10031,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N43" s="7" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9870,10 +10083,10 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9926,15 +10139,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="7" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9976,10 +10189,14 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" s="7" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr">
+        <is>
+          <t>페어아이작(FICO 신용점수·분석): 울프리서치가 밴티지스코어 경쟁 위협·정부프로그램 지연 이유로 아웃퍼폼→피어퍼폼 강등</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10030,14 +10247,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="7" t="inlineStr">
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>(전일) 아르시스(산업용 전자부품 롤업): 2Q 매출 25%·EBITDA 38% 성장, 연 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10086,15 +10303,15 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="7" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10138,10 +10355,10 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10190,19 +10407,19 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>(전일) 마스텍(통신·에너지 인프라 시공): 2Q 매출·가이던스 상향에도 EPS 컨센 미달로 하락</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10246,15 +10463,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="7" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10298,15 +10515,15 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="7" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10350,15 +10567,15 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" s="7" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10406,15 +10623,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="7" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10458,15 +10675,19 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr">
+        <is>
+          <t>블루아울(사모대출·대안자산운용): Q2 매출 $754M 컨센 9.6% 상회, 英 스파이어헬스케어 병원 13억파운드 인수 등 딜 발표로 급등</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10510,10 +10731,10 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" s="7" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10566,19 +10787,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="7" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>(전일) 존스랭라살(상업용 부동산 서비스): 2분기 조정EPS +61%·EBITDA +32%, 가이던스 상향에 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10620,15 +10841,15 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10676,15 +10897,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="7" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10728,15 +10949,15 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="7" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10780,10 +11001,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="7" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10830,15 +11051,15 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10884,15 +11105,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10940,15 +11161,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N64" s="7" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10988,15 +11209,19 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>유니티소프트웨어(게임엔진·3D툴): Q2 실적(8/5) 기대·전략매출 35% 성장 확인, 7/31 급락분 반등에 나스닥 강세 수혜</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11040,10 +11265,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11092,19 +11317,19 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 바코드·모바일컴퓨터): 소프트웨어·AI분석 수요 회복 기대, 목표가 연속 상향으로 신고가</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11152,10 +11377,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="7" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11202,15 +11427,15 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" s="7" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11254,15 +11479,15 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11306,10 +11531,14 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>CNH인더스트리얼(농기계·건설장비): Q2 EPS·매출 컨센 상회, FY26 EPS 가이던스 유지로 낙관 회복</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11358,15 +11587,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="7" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11410,15 +11639,15 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11466,15 +11695,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="7" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11516,10 +11745,10 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11572,15 +11801,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11620,15 +11849,19 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr">
+        <is>
+          <t>액솜테라퓨틱스(중추신경계 바이오): 미즈호 목표가 소폭 하향·Q1 손실폭 확대에 수익성 우려 지속</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11672,15 +11905,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11724,15 +11957,15 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11780,15 +12013,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N80" s="7" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11830,15 +12063,15 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="7" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11884,7 +12117,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="7" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N82"/>
@@ -11990,12 +12223,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12037,15 +12270,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중외제약(로슈 계열 항암제): 7/24 상반기 순이익 +19% 호조 후 재료 소진 매도 지속, 신저가 국면</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12089,15 +12326,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>스미토모전기(전선·자동차부품): Q1 영업이익 +61% 호조에도 자동차부문 원자재비 감익·자동차 섹터 동반 하락에 편승</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12141,15 +12382,19 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>파나크(FA·산업용 로봇): 7/31 Q1 영업이익 컨센 하회·연간 가이던스 상향폭 실망에 매도, 블룸버그 기준 약 40년 만 최대 낙폭</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12193,15 +12438,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>미쓰비시지쇼(대형 종합부동산): Q1 순이익 +23% 호조였으나 개별 촉매 없음, 美 금리 재상승 우려로 부동산 섹터 매도</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12245,15 +12494,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12297,15 +12546,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12349,7 +12598,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>아이신(자동차 부품·변속기): 7/31 Q1 영업이익 -23.6% 감익, 관세·원자재 비용 압박에 연속 하락</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N8"/>
@@ -12455,12 +12708,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12506,15 +12759,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>메이디그룹H(중국 최대 가전): 전환사채 전환가 인하로 H주 희석 우려 지속, 신고가 후 차익실현 매물에 하락 마감</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12558,10 +12815,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>중신궈지(중국 최대 파운드리): 국가반도체기금 연속 지분축소+PER 99배 밸류 부담+증권사 홀드 하향에 심리 위축 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12614,19 +12875,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 매뉴라이프(보험): 8/5 실적 대기 속 아시아 성장 기대, 특별 당일 촉매 없음(섹터 수급 추정)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12668,15 +12929,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>프라다(이탈리아 명품패션): 7/30 상반기 매출 +16%(불변환율)·Q2 유기성장 +7% 가속 확인 후 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12720,15 +12985,19 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>지투글로벌익스프레스(글로벌 택배물류): Q2 소포량 +24%·일평균 1억건 돌파, 6월 HK$20억 자사주매입 계획이 지지</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12772,10 +13041,14 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>젠카이라미네이트(PCB용 적층판): 특별한 뉴스 없음(6월 이후 누적 -60%+ 추세 속 섹터 수요둔화·수급 매물 소화)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12822,19 +13095,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) 우프부동산투자(홍콩 프리미엄 쇼핑몰·호텔 리츠): 특별한 뉴스 없음(부동산 수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12878,7 +13151,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>넥스칩반도체(디스플레이드라이버·이미지센서 파운드리): 7/10 상장 1개월 내 차익실현+성숙공정 과잉공급 우려로 신저가</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N9"/>
@@ -12984,12 +13261,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13033,15 +13310,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="7" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>리쉰정밀(애플 공급망 정밀부품): 8/3 애플체인·AI하드웨어 섹터 동반 약세로 수급 이탈</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13085,15 +13366,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>흥업은행(주요 주식제 은행): 저금리 속 배당수익률 6%+ 방어주 매력으로 시장 약세에서 상대 강세</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13141,15 +13426,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>하이크비전(보안카메라·AI영상): 상반기 영업이익 +39%·매출 +12% 호실적 발표 후 신고가 경신</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13193,10 +13482,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="7" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>코스코쉬핑(컨테이너 해운): 컨테이너 운임 3개월 연속 상승+중간배당 기대감으로 상승</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13245,14 +13538,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) 핑안은행(주식제 상업은행): 은행 섹터 상승 흐름, 고배당·PBR 0.4배대 저평가 순환매 수혜</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13301,19 +13594,19 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이국제항만(항만운영): 7/20 상반기 순이익 5.35% 증가 예고, 컨테이너 물동량 호조로 신고가</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13355,15 +13648,19 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="7" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>홍허커지(고급 전자소재·전자천): 특별한 뉴스 없음(전자소재 중소형주 약세 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13407,15 +13704,19 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>윈난바이야오(전통 한방·소비재): 특별한 뉴스 없음(소비재 약세 동반 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13459,15 +13760,19 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="7" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>통푸마이크로(반도체 후공정 패키징): 7/30 하한가 후 반등 실패+국가대기금 11.7%→5% 지분축소 진행에 연속 매도</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13509,15 +13814,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="7" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13559,15 +13864,19 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>하이다그룹(수산·사료): Q1 순이익 -30.8% 부진 지속, 약세장 동반 수급 이탈</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13609,15 +13918,15 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13661,15 +13970,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="7" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13713,15 +14022,19 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>이좡반도체(반도체 열처리 장비): 8/3 반도체 장비 섹터 집중 매도, 다수 종목 10%+ 하락에 동조</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13763,7 +14076,11 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>샤논반도체(반도체 유통·IP): 8/3 반도체·AI연산 하드웨어 섹터 전반 급락 속 동반 하락</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N16"/>
